--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,90 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,50 +749,53 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E8" s="3">
         <v>52500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>64000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>95700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>93200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>124400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>143600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>166300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>99100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>99800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>60000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>134300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,50 +814,53 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E9" s="3">
         <v>22200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>24200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>66200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,50 +879,53 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E10" s="3">
         <v>30300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>71500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>68700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>102000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>121500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>143100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>80600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>77900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>55100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>42100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +971,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,13 +1099,16 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>21300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1097,8 +1116,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1106,27 +1125,27 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>66600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,50 +1164,53 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E15" s="3">
         <v>16800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6900</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1207,8 +1229,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,58 +1253,59 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E17" s="3">
         <v>70100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>63500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>62700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>55800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>51200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>45700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>40700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>165600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1290,50 +1316,53 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>79100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>95800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>115100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>57100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>54100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,50 +1408,51 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E20" s="3">
         <v>14500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>11000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>3500</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,47 +1471,50 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>13700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>54800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>54000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>87400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>103400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>120500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>61800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>27900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,13 +1536,16 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="E22" s="3">
         <v>1400</v>
@@ -1515,35 +1554,35 @@
         <v>1400</v>
       </c>
       <c r="G22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>2600</v>
       </c>
       <c r="M22" s="3">
         <v>2600</v>
       </c>
       <c r="N22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1562,58 +1601,61 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>84100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>96600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>113300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>54700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>51600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1624,50 +1666,53 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-19900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>20900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>23400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-17600</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1686,8 +1731,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,58 +1796,61 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>37400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>67000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>63200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>73300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>85600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>42800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1810,58 +1861,61 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>37400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>67000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>63200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>73300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>85600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>49000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1872,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,50 +2186,53 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-11000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3500</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,58 +2251,61 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>37400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>67000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>63200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>73300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>85600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>49000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>42800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,58 +2381,61 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>37400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>67000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>63200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>73300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>85600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>49000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>42800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2368,64 +2446,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,58 +2568,59 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>263400</v>
+      </c>
+      <c r="E41" s="3">
         <v>547700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>927200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>651200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>428000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>664500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1233300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1179300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1179400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1196900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1181500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>519700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1400</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2545,32 +2631,35 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>734500</v>
+      </c>
+      <c r="E42" s="3">
         <v>537000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>200800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>517800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1045700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>836300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>599700</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2586,8 +2675,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2607,50 +2696,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E43" s="3">
         <v>17300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>35100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>37000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>37100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>51000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>37100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,50 +2761,53 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E44" s="3">
         <v>77200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>67800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>61800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>57600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>61600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>42200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>39600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>38700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>34100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>35500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>35100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>32300</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,58 +2826,61 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E45" s="3">
         <v>9200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>500</v>
       </c>
       <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>500</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2793,59 +2891,62 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1131200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1188300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1223900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1267400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1293800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1356800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1348900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1316500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1276800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1255500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1246100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1239100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>561000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>600</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,31 +2956,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>9700</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2893,18 +2997,18 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>345100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>345000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,50 +3021,53 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1168700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1108700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1055400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1002200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>935700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>830000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>749800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>668500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>611700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>584100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>562000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>534100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>503000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,17 +3086,20 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E49" s="3">
         <v>9200</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3005,8 +3115,8 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -3041,8 +3151,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,50 +3281,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E52" s="3">
         <v>16000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>9800</v>
       </c>
       <c r="M52" s="3">
         <v>9800</v>
       </c>
       <c r="N52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="O52" s="3">
         <v>9300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3346,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,59 +3411,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2336500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2322200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2289400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2281100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2237800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2189200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2101200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1987200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1889700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1849500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1818000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1782500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1074300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>346300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>346900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,59 +3528,60 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E57" s="3">
         <v>92100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>71700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>68600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>72300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>70200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>37700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,23 +3591,26 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2300</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -3488,32 +3621,32 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>16300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>31200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>46100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>41800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,55 +3656,58 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>100</v>
       </c>
       <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3">
+        <v>100</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3585,59 +3721,62 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E60" s="3">
         <v>97000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>75800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>66100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>70800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>90300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>72900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>43100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,50 +3786,53 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E61" s="3">
         <v>684700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>684100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>683500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>678400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>677600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>676700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>675800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>675500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>674700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>673800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>691000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>46100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3709,55 +3851,58 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>177100</v>
+      </c>
+      <c r="E62" s="3">
         <v>164500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>164600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>151900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>149200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>194500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>187700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>169500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>145900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>149800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>147200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>143400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>131300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>12100</v>
       </c>
       <c r="Q62" s="3">
         <v>12100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>12100</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -3771,8 +3916,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,59 +4111,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>970700</v>
+      </c>
+      <c r="E66" s="3">
         <v>946100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>924500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>929300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>925200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>946900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>930500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>896800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>880900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>895300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>911300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>907400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>220400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,58 +4461,61 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>385700</v>
+      </c>
+      <c r="E72" s="3">
         <v>402000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>406300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>398900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>361400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>294400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>231200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>158000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>72400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-46500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-62600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4353,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,58 +4721,61 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1365800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1376100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1364900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1351800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1312600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1242300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1170700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1090400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1008700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>954200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>906600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>875200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>853900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>330700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>333800</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4601,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,64 +4851,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,58 +4921,61 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>37400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>67000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>63200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>73300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>85600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>49000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>42800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4792,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,47 +5013,48 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E83" s="3">
         <v>16800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4872,14 +5070,17 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,58 +5401,61 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E89" s="3">
         <v>11000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>55500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>94600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>98900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>121000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>38600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,47 +5493,48 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-74500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-112300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-91700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19300</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5330,14 +5550,17 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,52 +5686,55 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-269100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-390300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>265900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>462200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-315200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-325100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-666800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-49800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>322600</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5522,8 +5751,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5608,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,58 +6036,61 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>671800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>175200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>346800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -5856,8 +6101,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5918,58 +6166,61 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-284300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-380200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>275100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>510900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-290900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-231200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-568800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>53300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>662000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>502000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -5978,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,53 +753,56 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E8" s="3">
         <v>41200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>52500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>64000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>95700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>93200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>124400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>143600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>166300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>99100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>99800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>73100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>60000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>134300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -817,53 +821,56 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E9" s="3">
         <v>23600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,53 +889,56 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E10" s="3">
         <v>17600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>68700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>102000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>121500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>143100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>80600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>55100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,31 +985,32 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>4200</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="F12" s="3">
+        <v>10200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2700</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,25 +1119,28 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="E14" s="3">
         <v>21300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1128,27 +1148,27 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>66600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1167,53 +1187,56 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E15" s="3">
         <v>18600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6900</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,61 +1280,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E17" s="3">
         <v>74800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>70100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>63500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>62700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>55800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>165600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1319,53 +1346,56 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-33600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>33000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>37400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>79100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>95800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>115100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>57100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>54100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,53 +1442,54 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E20" s="3">
         <v>14100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>3500</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,50 +1508,53 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>54800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>54000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>87400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>103400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>120500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>42600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>27900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,16 +1576,19 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1400</v>
       </c>
       <c r="F22" s="3">
         <v>1400</v>
@@ -1557,35 +1597,35 @@
         <v>1400</v>
       </c>
       <c r="H22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>2600</v>
       </c>
       <c r="N22" s="3">
         <v>2600</v>
       </c>
       <c r="O22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1604,61 +1644,64 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>45300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>84100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>96600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>113300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>54700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>51600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1669,53 +1712,56 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-19900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>20900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>23400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,61 +1848,64 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>67000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>63200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>73300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>85600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1864,61 +1916,64 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>67000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>63200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>73300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>85600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>49000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,53 +2256,56 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-3500</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,61 +2324,64 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>67000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>63200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>73300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>85600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>49000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,61 +2460,64 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>67000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>63200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>73300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>85600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>49000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2449,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,61 +2655,62 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>296500</v>
+      </c>
+      <c r="E41" s="3">
         <v>263400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>547700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>927200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>651200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>136600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>428000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>664500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1233300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1179300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1179400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1196900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1181500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>519700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1400</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2634,35 +2721,38 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>650300</v>
+      </c>
+      <c r="E42" s="3">
         <v>734500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>537000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>200800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>517800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1045700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>836300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>599700</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2678,8 +2768,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2699,53 +2789,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E43" s="3">
         <v>29300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>35100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>37000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>51000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,53 +2857,56 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E44" s="3">
         <v>95200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>77200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>67800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>61800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>57600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>61600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>42200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>39600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>38700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>34100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>35500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>35100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>32300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2829,61 +2925,64 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="3">
         <v>8800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>500</v>
       </c>
       <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>500</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -2894,62 +2993,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1106200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1131200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1188300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1223900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1267400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1293800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1356800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1348900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1316500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1276800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1255500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1246100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1239100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>561000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>600</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,17 +3061,20 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E47" s="3">
         <v>9700</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2985,8 +3090,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3000,18 +3105,18 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>345100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>345000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,53 +3129,56 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1206700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1168700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1108700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1055400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1002200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>935700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>830000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>749800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>668500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>611700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>584100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>562000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>534100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>503000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,20 +3197,23 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E49" s="3">
         <v>8900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9200</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3118,8 +3229,8 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,53 +3401,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E52" s="3">
         <v>18000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>9800</v>
       </c>
       <c r="N52" s="3">
         <v>9800</v>
       </c>
       <c r="O52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="P52" s="3">
         <v>9300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,62 +3537,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2354000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2336500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2322200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2289400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2281100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2237800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2189200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2101200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1987200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1889700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1849500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1818000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1782500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1074300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>346300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>346900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>600</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,62 +3659,63 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E57" s="3">
         <v>28000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>92100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>68600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>72300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>70200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>37700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,26 +3725,29 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2300</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3624,32 +3758,32 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>16300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>31200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>41800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>24700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,58 +3793,61 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E59" s="3">
         <v>78300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>100</v>
       </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+      <c r="S59" s="3">
+        <v>100</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3724,62 +3861,65 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>107500</v>
+      </c>
+      <c r="E60" s="3">
         <v>108600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>66100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>59500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>70800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>72900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>43100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,53 +3929,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>937700</v>
+      </c>
+      <c r="E61" s="3">
         <v>685000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>684700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>684100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>683500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>678400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>677600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>676700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>675800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>675500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>674700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>673800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>691000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>46100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3854,58 +3997,61 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E62" s="3">
         <v>177100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>164500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>164600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>151900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>149200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>194500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>187700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>169500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>145900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>149800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>147200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>143400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>131300</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>12100</v>
       </c>
       <c r="R62" s="3">
         <v>12100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>12100</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,62 +4269,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1216300</v>
+      </c>
+      <c r="E66" s="3">
         <v>970700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>946100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>924500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>929300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>925200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>946900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>930500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>896800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>880900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>895300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>911300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>907400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>220400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,61 +4635,64 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>402200</v>
+      </c>
+      <c r="E72" s="3">
         <v>385700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>402000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>406300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>398900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>361400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>294400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>231200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>158000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>72400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-19300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-46500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-62600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,61 +4907,64 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1137800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1365800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1376100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1364900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1351800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1312600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1242300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1170700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1090400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1008700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>954200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>906600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>875200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>853900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>330700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>333800</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,61 +5116,64 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>67000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>63200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>73300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>85600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>49000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,50 +5212,51 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E83" s="3">
         <v>18600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5073,14 +5272,17 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,61 +5618,64 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>55500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>94600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>98900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>121000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>38600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,50 +5714,51 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-73000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-74500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-112300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-91700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-67700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19300</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5553,14 +5774,17 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,55 +5916,58 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-269100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-390300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>265900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>462200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-315200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-325100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-666800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-49800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>322600</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,61 +6282,64 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>671800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>175200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>346800</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -6104,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6169,61 +6418,64 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-284300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-380200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>275100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>510900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-290900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-231200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-568800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>662000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>502000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,56 +757,59 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E8" s="3">
         <v>48700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>52500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>64000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>95700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>93200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>124400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>143600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>166300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>99100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>99800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>73100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>60000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>134300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -824,56 +828,59 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E9" s="3">
         <v>35600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>23200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>66200</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,56 +899,59 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E10" s="3">
         <v>13100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>68700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>102000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>121500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>143100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>80600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>77900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>55100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>42100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>68100</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,35 +999,36 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>4200</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
         <v>10200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,28 +1139,31 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-45000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>21300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1151,27 +1171,27 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>66600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,56 +1210,59 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E15" s="3">
         <v>18400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6900</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,64 +1307,65 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E17" s="3">
         <v>34900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>74800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>70100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>63500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>62700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>165600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1349,56 +1376,59 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="E18" s="3">
         <v>13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>37400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>79100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>95800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>115100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>57100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>54100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>21700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31300</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,56 +1476,57 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="3">
         <v>12600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>14500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>13700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>3500</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1511,53 +1545,56 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E21" s="3">
         <v>44900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>54800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>87400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>103400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>120500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>42600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,19 +1616,22 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1400</v>
       </c>
       <c r="G22" s="3">
         <v>1400</v>
@@ -1600,35 +1640,35 @@
         <v>1400</v>
       </c>
       <c r="I22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>2600</v>
       </c>
       <c r="O22" s="3">
         <v>2600</v>
       </c>
       <c r="P22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5000</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1647,64 +1687,67 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48200</v>
+      </c>
+      <c r="E23" s="3">
         <v>23600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>45300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>47100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>84100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>96600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>113300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>54700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>51600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1715,56 +1758,59 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E24" s="3">
         <v>7100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-19900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>23400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-17600</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,64 +1900,67 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E26" s="3">
         <v>16500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>67000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>63200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>73300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>85600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>42800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1919,64 +1971,67 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E27" s="3">
         <v>16500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>67000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>63200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>73300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>85600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>49000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,56 +2326,59 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-14500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-13700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-3500</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,64 +2397,67 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E33" s="3">
         <v>16500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>37400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>67000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>63200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>73300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>85600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>49000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,64 +2539,67 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E35" s="3">
         <v>16500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>37400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>67000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>63200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>73300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>85600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>49000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2531,70 +2610,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2686,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,64 +2742,65 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>295600</v>
+      </c>
+      <c r="E41" s="3">
         <v>296500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>263400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>547700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>927200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>651200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>136600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>428000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>664500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1233300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1179300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1179400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1196900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1181500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>519700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1400</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2724,38 +2811,41 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>641400</v>
+      </c>
+      <c r="E42" s="3">
         <v>650300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>734500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>537000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>200800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>517800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1045700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>836300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>599700</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2771,8 +2861,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2792,56 +2882,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E43" s="3">
         <v>40900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>35100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>37100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>51000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,56 +2953,59 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E44" s="3">
         <v>108500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>95200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>77200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>67800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>61800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>57600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>61600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>42200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>39600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>38700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>34100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>35500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>35100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>32300</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,64 +3024,67 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E45" s="3">
         <v>10000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>500</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>500</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -2996,65 +3095,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1090600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1106200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1131200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1188300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1223900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1267400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1293800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1356800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1348900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1316500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1276800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1255500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1246100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1239100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>561000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>600</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,20 +3166,23 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E47" s="3">
         <v>9600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9700</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3198,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3108,18 +3213,18 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>345100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>345000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3132,56 +3237,59 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1226900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1206700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1168700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1108700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1055400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1002200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>935700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>830000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>749800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>668500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>611700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>584100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>562000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>534100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>503000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,23 +3308,26 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E49" s="3">
         <v>8600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9200</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3232,8 +3343,8 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,56 +3521,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E52" s="3">
         <v>22900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>9800</v>
       </c>
       <c r="O52" s="3">
         <v>9800</v>
       </c>
       <c r="P52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Q52" s="3">
         <v>9300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,65 +3663,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2364300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2354000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2336500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2322200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2289400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2281100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2237800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2189200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2101200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1987200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1889700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1849500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1818000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1782500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1074300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>346300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>346900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>600</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,65 +3790,66 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E57" s="3">
         <v>26100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>92100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>71700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>68600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>72300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>70200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,29 +3859,32 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -3761,32 +3895,32 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>16300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>31200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>46100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>24700</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3796,61 +3930,64 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>136100</v>
+      </c>
+      <c r="E59" s="3">
         <v>79300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>78300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
-      </c>
-      <c r="R59" s="3">
-        <v>100</v>
       </c>
       <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
+      <c r="T59" s="3">
+        <v>100</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
@@ -3864,65 +4001,68 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>158100</v>
+      </c>
+      <c r="E60" s="3">
         <v>107500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>108600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>97000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>75800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>97500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>74700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>66100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>70800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>90300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>72900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>43100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,56 +4072,59 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>938500</v>
+      </c>
+      <c r="E61" s="3">
         <v>937700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>685000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>684700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>684100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>683500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>678400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>677600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>676700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>675800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>675500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>674700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>673800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>691000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4000,61 +4143,64 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>158700</v>
+      </c>
+      <c r="E62" s="3">
         <v>171000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>177100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>164500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>164600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>151900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>149200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>194500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>187700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>169500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>145900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>149800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>147200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>143400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>131300</v>
-      </c>
-      <c r="R62" s="3">
-        <v>12100</v>
       </c>
       <c r="S62" s="3">
         <v>12100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>12100</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,65 +4427,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1255300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1216300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>970700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>946100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>924500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>929300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>925200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>946900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>930500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>896800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>880900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>895300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>911300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>907400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>220400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,64 +4809,67 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>368200</v>
+      </c>
+      <c r="E72" s="3">
         <v>402200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>385700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>402000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>406300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>398900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>361400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>294400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>231200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>158000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>72400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-19300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-46500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-62600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-300</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,64 +5093,67 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1109000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1137800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1365800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1376100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1364900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1351800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1312600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1242300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1170700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1090400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1008700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>954200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>906600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>875200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>853900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>330700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>333800</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5235,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,64 +5311,67 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E81" s="3">
         <v>16500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>37400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>67000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>63200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>73300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>85600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>49000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,53 +5411,54 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E83" s="3">
         <v>18400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5275,14 +5474,17 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,64 +5835,67 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-41100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>55500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>94600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>98900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>121000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>38600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,53 +5935,54 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-73000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-74500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-112300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-91700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-67700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-54900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5777,14 +5998,17 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,58 +6146,61 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E94" s="3">
         <v>40700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-269100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-390300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>265900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>462200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-315200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-325100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-666800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-49800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-39100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>322600</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,64 +6528,67 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>32900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>671800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>175200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>346800</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6353,8 +6599,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6421,64 +6670,67 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>32500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-284300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-380200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>275100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>510900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-290900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-231200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-568800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>53300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>662000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>502000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1400</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,59 +761,62 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E8" s="3">
         <v>31300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>48700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>52500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>64000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>95700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>93200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>124400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>143600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>166300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>99100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>99800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>73100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>60000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>134300</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,59 +835,62 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E9" s="3">
         <v>41500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>23600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>23200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>66200</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,59 +909,62 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-10200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>17600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>71500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>68700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>102000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>121500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>143100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>80600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>77900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>42100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>68100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,38 +1013,39 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
-        <v>4200</v>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="3">
-        <v>10200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>8300</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>5600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,31 +1159,34 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2300</v>
+        <v>1900</v>
       </c>
       <c r="E14" s="3">
-        <v>-45000</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>-44800</v>
+      </c>
+      <c r="G14" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H14" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>6400</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1174,27 +1194,27 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>66600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,59 +1233,62 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E15" s="3">
         <v>18200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6900</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,67 +1334,68 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>84800</v>
+        <v>100600</v>
       </c>
       <c r="E17" s="3">
-        <v>34900</v>
+        <v>83200</v>
       </c>
       <c r="F17" s="3">
-        <v>74800</v>
+        <v>79700</v>
       </c>
       <c r="G17" s="3">
-        <v>70100</v>
+        <v>68500</v>
       </c>
       <c r="H17" s="3">
-        <v>63500</v>
+        <v>61900</v>
       </c>
       <c r="I17" s="3">
-        <v>62700</v>
+        <v>57100</v>
       </c>
       <c r="J17" s="3">
+        <v>55600</v>
+      </c>
+      <c r="K17" s="3">
         <v>55800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>45300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>45700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>165600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
@@ -1379,59 +1406,62 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-53500</v>
+        <v>-37600</v>
       </c>
       <c r="E18" s="3">
-        <v>13800</v>
+        <v>-52000</v>
       </c>
       <c r="F18" s="3">
-        <v>-33600</v>
+        <v>-31000</v>
       </c>
       <c r="G18" s="3">
-        <v>-17600</v>
+        <v>-27300</v>
       </c>
       <c r="H18" s="3">
-        <v>500</v>
+        <v>-9400</v>
       </c>
       <c r="I18" s="3">
-        <v>33000</v>
+        <v>6900</v>
       </c>
       <c r="J18" s="3">
+        <v>40100</v>
+      </c>
+      <c r="K18" s="3">
         <v>37400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>79100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>95800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>115100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>57100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>54100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>21700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-31300</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1480,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,59 +1510,60 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>12000</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>12600</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>14100</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>14500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>13800</v>
+        <v>300</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>11000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>3500</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,56 +1582,59 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-23200</v>
+        <v>-18700</v>
       </c>
       <c r="E21" s="3">
-        <v>44900</v>
+        <v>-34100</v>
       </c>
       <c r="F21" s="3">
-        <v>-900</v>
+        <v>-12800</v>
       </c>
       <c r="G21" s="3">
-        <v>13700</v>
+        <v>-9000</v>
       </c>
       <c r="H21" s="3">
-        <v>26500</v>
+        <v>7400</v>
       </c>
       <c r="I21" s="3">
-        <v>54800</v>
+        <v>19100</v>
       </c>
       <c r="J21" s="3">
+        <v>48200</v>
+      </c>
+      <c r="K21" s="3">
         <v>54000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>87400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>103400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>120500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,22 +1656,25 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E22" s="3">
         <v>6700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1400</v>
       </c>
       <c r="H22" s="3">
         <v>1400</v>
@@ -1643,35 +1683,35 @@
         <v>1400</v>
       </c>
       <c r="J22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>2600</v>
       </c>
       <c r="P22" s="3">
         <v>2600</v>
       </c>
       <c r="Q22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5000</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1690,67 +1730,70 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-20700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>47100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>84100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>96600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>113300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>54700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>51600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-36100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
@@ -1761,59 +1804,62 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-19900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>23400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>27800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-17600</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,67 +1952,70 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>37400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>67000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>63200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>73300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>85600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>42800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
@@ -1974,67 +2026,70 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>37400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>67000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>63200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>85600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>49000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>42800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
@@ -2045,8 +2100,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,59 +2396,62 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12000</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>-12600</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>-14100</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-13800</v>
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
-        <v>-13700</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-11000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,67 +2470,70 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>37400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>67000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>63200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>73300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>85600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>49000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>42800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2544,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,67 +2618,70 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>37400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>67000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>63200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>73300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>85600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>49000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>42800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
@@ -2613,73 +2692,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2771,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,67 +2829,68 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>284400</v>
+      </c>
+      <c r="E41" s="3">
         <v>295600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>296500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>263400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>547700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>927200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>651200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>428000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>664500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1233300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1179300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1179400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1196900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1181500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>519700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1400</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
+      <c r="V41" s="3">
+        <v>0</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
@@ -2814,41 +2901,44 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>582100</v>
+      </c>
+      <c r="E42" s="3">
         <v>641400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>650300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>734500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>537000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>200800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>517800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1045700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>836300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>599700</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2864,8 +2954,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2885,59 +2975,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E43" s="3">
         <v>27800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>40900</v>
       </c>
-      <c r="F43" s="3">
-        <v>29300</v>
-      </c>
       <c r="G43" s="3">
+        <v>30200</v>
+      </c>
+      <c r="H43" s="3">
         <v>17300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>37000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>51000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3600</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,59 +3049,62 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E44" s="3">
         <v>115400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>108500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>95200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>77200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>67800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>61800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>57600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>61600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>42200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>39600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>38700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>34100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>35500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>35100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>32300</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,67 +3123,70 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>10400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>10000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>12800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>13600</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>18900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
-      </c>
-      <c r="T45" s="3">
-        <v>500</v>
       </c>
       <c r="U45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
+      <c r="V45" s="3">
+        <v>500</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
@@ -3098,68 +3197,71 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1017200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1090600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1106200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1131200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1188300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1223900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1267400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1293800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1356800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1348900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1316500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1276800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1255500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1246100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1239100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>561000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>600</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,23 +3271,26 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E47" s="3">
         <v>9300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9700</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,8 +3306,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3216,18 +3321,18 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>345100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>345000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,59 +3345,62 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1240500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1226900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1206700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1168700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1108700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1055400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1002200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>935700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>830000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>749800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>668500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>611700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>584100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>562000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>534100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>503000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,31 +3419,34 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -3346,8 +3457,8 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,59 +3641,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E52" s="3">
         <v>29200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>9800</v>
       </c>
       <c r="P52" s="3">
         <v>9800</v>
       </c>
       <c r="Q52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="R52" s="3">
         <v>9300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,68 +3789,71 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2300300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2364300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2354000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2336500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2322200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2289400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2281100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2237800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2189200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2101200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1987200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1889700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1849500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1818000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1782500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1074300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>346300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>346900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,68 +3921,69 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E57" s="3">
         <v>19800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>92100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>71700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>68600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>72300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>70200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>37700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,32 +3993,35 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2200</v>
+        <v>3700</v>
       </c>
       <c r="E58" s="3">
-        <v>2100</v>
+        <v>3200</v>
       </c>
       <c r="F58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="G58" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -3898,32 +4032,32 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>16300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>31200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>46100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>41800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>24700</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,64 +4067,67 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>136100</v>
+        <v>89900</v>
       </c>
       <c r="E59" s="3">
-        <v>79300</v>
+        <v>111600</v>
       </c>
       <c r="F59" s="3">
-        <v>78300</v>
+        <v>59300</v>
       </c>
       <c r="G59" s="3">
-        <v>2500</v>
+        <v>49800</v>
       </c>
       <c r="H59" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J59" s="3">
         <v>23000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2200</v>
-      </c>
-      <c r="S59" s="3">
-        <v>100</v>
       </c>
       <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+      <c r="U59" s="3">
+        <v>100</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
@@ -4004,68 +4141,71 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>146800</v>
+      </c>
+      <c r="E60" s="3">
         <v>158100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>107500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>108600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>93900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>97500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>74700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>66100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>59500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>70800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>90300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>72900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>43100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,59 +4215,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>938500</v>
+        <v>945200</v>
       </c>
       <c r="E61" s="3">
-        <v>937700</v>
+        <v>944800</v>
       </c>
       <c r="F61" s="3">
-        <v>685000</v>
+        <v>944600</v>
       </c>
       <c r="G61" s="3">
-        <v>684700</v>
+        <v>691800</v>
       </c>
       <c r="H61" s="3">
-        <v>684100</v>
+        <v>691700</v>
       </c>
       <c r="I61" s="3">
+        <v>691200</v>
+      </c>
+      <c r="J61" s="3">
         <v>683500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>678400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>677600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>676700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>675800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>675500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>674700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>673800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>691000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>46100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4146,64 +4289,67 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>158700</v>
+        <v>25400</v>
       </c>
       <c r="E62" s="3">
-        <v>171000</v>
+        <v>25900</v>
       </c>
       <c r="F62" s="3">
-        <v>177100</v>
+        <v>23900</v>
       </c>
       <c r="G62" s="3">
-        <v>164500</v>
+        <v>22100</v>
       </c>
       <c r="H62" s="3">
-        <v>164600</v>
+        <v>22000</v>
       </c>
       <c r="I62" s="3">
-        <v>151900</v>
+        <v>22000</v>
       </c>
       <c r="J62" s="3">
+        <v>22200</v>
+      </c>
+      <c r="K62" s="3">
         <v>149200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>194500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>187700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>169500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>145900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>149800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>147200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>143400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>131300</v>
-      </c>
-      <c r="S62" s="3">
-        <v>12100</v>
       </c>
       <c r="T62" s="3">
         <v>12100</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>12100</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,68 +4585,71 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1235700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1255300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1216300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>970700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>946100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>924500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>929300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>925200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>946900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>930500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>896800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>880900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>895300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>911300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>907400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>220400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,67 +4983,70 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>342600</v>
+      </c>
+      <c r="E72" s="3">
         <v>368200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>402200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>385700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>402000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>406300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>398900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>361400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>294400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>231200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>158000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>72400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>23400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-46500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-62600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-300</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,67 +5279,70 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1064500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1109000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1137800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1365800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1376100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1364900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1351800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1312600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1242300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1170700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1090400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1008700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>954200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>906600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>875200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>853900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>330700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>333800</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,73 +5427,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,67 +5506,70 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>37400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>67000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>63200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>73300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>85600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>49000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>42800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
@@ -5385,8 +5580,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,56 +5610,57 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>18200</v>
+        <v>16700</v>
       </c>
       <c r="E83" s="3">
-        <v>18400</v>
+        <v>12000</v>
       </c>
       <c r="F83" s="3">
-        <v>18600</v>
+        <v>8100</v>
       </c>
       <c r="G83" s="3">
-        <v>16800</v>
+        <v>5600</v>
       </c>
       <c r="H83" s="3">
-        <v>12200</v>
+        <v>2100</v>
       </c>
       <c r="I83" s="3">
-        <v>8100</v>
+        <v>5400</v>
       </c>
       <c r="J83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5477,14 +5676,17 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,67 +6052,70 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E89" s="3">
         <v>30800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>55500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>94600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>98900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>121000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>38600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,56 +6156,57 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-73000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-74500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-112300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-91700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-67700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-54900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6001,14 +6222,17 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,61 +6376,64 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>40700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-269100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-390300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>265900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>462200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-315200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-325100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-666800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-49800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-39100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>322600</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,31 +6480,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,67 +6774,70 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>32900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>671800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>175200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>346800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6602,31 +6848,34 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6673,67 +6922,70 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-284300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-380200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>275100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>510900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-290900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-231200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-568800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>662000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>502000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1400</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,105 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -764,62 +764,65 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E8" s="3">
         <v>62900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>31300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>48700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>52500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>64000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>95700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>93200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>124400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>143600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>166300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>99100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>99800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>73100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>60000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>134300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -838,62 +841,65 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E9" s="3">
         <v>57300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>41500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66200</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,62 +918,65 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-10200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>102000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>121500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>143100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>80600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>77900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>42100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>68100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -986,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,8 +1026,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,15 +1053,15 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
         <v>5600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,62 +1178,65 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-44800</v>
       </c>
-      <c r="G14" s="3">
-        <v>5900</v>
-      </c>
       <c r="H14" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I14" s="3">
         <v>8200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>66600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1236,62 +1255,65 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E15" s="3">
         <v>19300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6900</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1310,8 +1332,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,70 +1360,71 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E17" s="3">
         <v>100600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>83200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>79700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>68500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>61900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>45300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>51200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>45700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>165600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1409,62 +1435,65 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-52000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-31000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-27300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>40100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>79100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>95800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>115100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>57100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>54100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-31300</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,62 +1543,63 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>300</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>11000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>3500</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,59 +1618,62 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-34100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-9000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I21" s="3">
         <v>7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>48200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>54000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>87400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>103400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>120500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>61100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>42600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>27900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,25 +1695,28 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E22" s="3">
         <v>6600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1400</v>
       </c>
       <c r="I22" s="3">
         <v>1400</v>
@@ -1686,35 +1725,35 @@
         <v>1400</v>
       </c>
       <c r="K22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>2600</v>
       </c>
       <c r="Q22" s="3">
         <v>2600</v>
       </c>
       <c r="R22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S22" s="3">
         <v>1200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5000</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1733,70 +1772,73 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-48200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>45300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>47100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>84100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>96600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>113300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>54700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>51600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1807,62 +1849,65 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-9400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-19900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>27800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-17600</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1881,8 +1926,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,70 +2003,73 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-16300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>37400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>67000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>63200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>85600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>42800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -2029,70 +2080,73 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-16300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>37400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>67000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>63200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>73300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>85600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>49000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>42800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2103,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,62 +2465,65 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-11000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-3500</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,70 +2542,73 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-16300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>37400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>67000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>63200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>73300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>85600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>49000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>42800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2547,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,70 +2696,73 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-16300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>37400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>67000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>63200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>73300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>85600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>49000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>42800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2695,76 +2773,79 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,70 +2915,71 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>282400</v>
+      </c>
+      <c r="E41" s="3">
         <v>284400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>295600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>296500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>263400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>547700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>927200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>651200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>136600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>428000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>664500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1233300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1179300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1179400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1196900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1181500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>519700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1400</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+      <c r="W41" s="3">
+        <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -2904,44 +2990,47 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>568400</v>
+      </c>
+      <c r="E42" s="3">
         <v>582100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>641400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>650300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>734500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>537000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>200800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>517800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1045700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>836300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>599700</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3046,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2978,62 +3067,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E43" s="3">
         <v>25800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40900</v>
       </c>
-      <c r="G43" s="3">
-        <v>30200</v>
-      </c>
       <c r="H43" s="3">
+        <v>31100</v>
+      </c>
+      <c r="I43" s="3">
         <v>17300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>51000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>37100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3600</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,62 +3144,65 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E44" s="3">
         <v>116700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>115400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>108500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>95200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>77200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>67800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>61800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>57600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>61600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>42200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>39600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>38700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>34100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>35500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>35100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>32300</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3126,8 +3221,11 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3152,44 +3250,44 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>18900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
-      </c>
-      <c r="U45" s="3">
-        <v>500</v>
       </c>
       <c r="V45" s="3">
         <v>500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
+      <c r="W45" s="3">
+        <v>500</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
@@ -3200,71 +3298,74 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1031300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1017200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1090600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1106200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1131200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1188300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1223900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1267400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1293800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1356800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1348900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1316500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1276800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1255500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1246100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1239100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>561000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>600</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,26 +3375,29 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E47" s="3">
         <v>9000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9700</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3309,8 +3413,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3324,18 +3428,18 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>345100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>345000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,62 +3452,65 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1261100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1240500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1226900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1206700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1168700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1108700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1055400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1002200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>935700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>830000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>749800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>668500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>611700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>584100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>562000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>534100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>503000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,34 +3529,37 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E49" s="3">
         <v>8000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9200</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -3460,8 +3570,8 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3496,8 +3606,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,62 +3760,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E52" s="3">
         <v>25600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>9800</v>
       </c>
       <c r="Q52" s="3">
         <v>9800</v>
       </c>
       <c r="R52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="S52" s="3">
         <v>9300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,71 +3914,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2333600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2300300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2364300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2354000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2336500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2322200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2289400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2281100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2237800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2189200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2101200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1987200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1889700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1849500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1818000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1782500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1074300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>346300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>346900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,71 +4051,72 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E57" s="3">
         <v>21700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>92100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>71700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>68600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>72300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>70200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>37700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4126,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4005,26 +4138,26 @@
         <v>3700</v>
       </c>
       <c r="E58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4035,32 +4168,32 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>16300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>31200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>46100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>41800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>24700</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,67 +4203,70 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>98500</v>
+      </c>
+      <c r="E59" s="3">
         <v>89900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>111600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59300</v>
       </c>
-      <c r="G59" s="3">
-        <v>49800</v>
-      </c>
       <c r="H59" s="3">
+        <v>49400</v>
+      </c>
+      <c r="I59" s="3">
         <v>1800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2200</v>
-      </c>
-      <c r="T59" s="3">
-        <v>100</v>
       </c>
       <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
+      <c r="V59" s="3">
+        <v>100</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
@@ -4144,71 +4280,74 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E60" s="3">
         <v>146800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>158100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>107500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>108600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>75800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>93900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>97500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>74700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>66100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>70800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>90300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,62 +4357,65 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>915300</v>
+      </c>
+      <c r="E61" s="3">
         <v>945200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>944800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>944600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>691800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>691700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>691200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>683500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>678400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>677600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>676700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>675800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>675500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>674700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>673800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>691000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4292,8 +4434,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4301,58 +4446,58 @@
         <v>25400</v>
       </c>
       <c r="E62" s="3">
+        <v>25400</v>
+      </c>
+      <c r="F62" s="3">
         <v>25900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>22000</v>
       </c>
       <c r="I62" s="3">
         <v>22000</v>
       </c>
       <c r="J62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="K62" s="3">
         <v>22200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>149200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>194500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>187700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>169500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>145900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>149800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>147200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>143400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>131300</v>
-      </c>
-      <c r="T62" s="3">
-        <v>12100</v>
       </c>
       <c r="U62" s="3">
         <v>12100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>12100</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
@@ -4366,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,71 +4742,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1278700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1235700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1255300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1216300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>970700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>946100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>924500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>929300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>925200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>946900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>930500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>896800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>880900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>895300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>911300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>907400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>220400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,70 +5156,73 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>320300</v>
+      </c>
+      <c r="E72" s="3">
         <v>342600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>368200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>402200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>385700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>402000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>406300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>398900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>361400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>294400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>231200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>158000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>72400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>23400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-19300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-46500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-62600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-300</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -5060,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,70 +5464,73 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1054900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1064500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1109000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1137800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1365800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1376100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1364900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1351800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1312600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1242300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1170700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1090400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1008700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>954200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>906600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>875200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>853900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>330700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>333800</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5356,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,76 +5618,79 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5509,70 +5700,73 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-16300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>37400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>67000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>63200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>73300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>85600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>49000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>42800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5583,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,59 +5808,60 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E83" s="3">
         <v>16700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5679,14 +5877,17 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,70 +6268,73 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-41100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>55500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>94600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>98900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>121000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>38600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -6129,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,59 +6376,60 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-51800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-73000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-74500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-112300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-91700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-67700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-54900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19300</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6225,14 +6445,17 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,64 +6605,67 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E94" s="3">
         <v>20700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>40700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-269100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-390300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>265900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>462200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-315200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-325100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-666800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-39100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>322600</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6453,8 +6682,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6507,8 +6740,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6555,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,70 +7019,73 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>32900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>671800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>175200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>346800</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -6851,8 +7096,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6877,8 +7125,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6925,70 +7173,73 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-284300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-380200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>275100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>510900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-290900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-231200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-568800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>662000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>502000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1400</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
@@ -6997,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,65 +768,68 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E8" s="3">
         <v>61000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>31300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>48700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>52500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>64000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>95700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>93200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>124400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>143600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>166300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>99100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>99800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>73100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>60000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>134300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,65 +848,68 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E9" s="3">
         <v>58300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>57300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>41500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>66200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,65 +928,68 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-10200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>30300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>68700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>102000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>121500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>143100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>80600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>77900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>55100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>42100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>68100</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,8 +1040,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,15 +1070,15 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
         <v>5600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,65 +1198,68 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-44800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>66600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,65 +1278,68 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E15" s="3">
         <v>22100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6900</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,73 +1387,74 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E17" s="3">
         <v>102500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>100600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>83200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>79700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>68500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>61900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>57100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>47800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>45700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>165600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1438,65 +1465,68 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-41500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-37600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-52000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-31000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-27300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>37400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>79100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>95800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>115100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>57100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>54100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-31300</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,65 +1577,66 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-6700</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>11000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>3500</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,62 +1655,65 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-19400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-34100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>54000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>87400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>103400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>120500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>61800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,28 +1735,31 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E22" s="3">
         <v>6800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1400</v>
       </c>
       <c r="J22" s="3">
         <v>1400</v>
@@ -1728,35 +1768,35 @@
         <v>1400</v>
       </c>
       <c r="L22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>2600</v>
       </c>
       <c r="R22" s="3">
         <v>2600</v>
       </c>
       <c r="S22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="T22" s="3">
         <v>1200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5000</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,73 +1815,76 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-48200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>84100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>96600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>113300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>54700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>51600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-36100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1852,65 +1895,68 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-9400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-14100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-19900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>27800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-17600</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,73 +2055,76 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>67000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>73300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>85600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>42800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2083,73 +2135,76 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>67000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>63200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>73300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>85600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>49000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>42800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,65 +2535,68 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-11000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-3500</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,73 +2615,76 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>67000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>63200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>73300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>85600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>49000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>42800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,73 +2775,76 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>67000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>63200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>73300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>85600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>49000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>42800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2776,79 +2855,82 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,73 +3002,74 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E41" s="3">
         <v>282400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>284400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>295600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>296500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>263400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>547700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>927200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>651200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>136600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>428000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>664500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1233300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1179300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1179400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1196900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1181500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>519700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1400</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
+      <c r="X41" s="3">
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
@@ -2993,47 +3080,50 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>560800</v>
+      </c>
+      <c r="E42" s="3">
         <v>568400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>582100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>641400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>650300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>734500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>537000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>200800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>517800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1045700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>836300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>599700</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3049,8 +3139,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3070,65 +3160,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E43" s="3">
         <v>62900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>35100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>51000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3600</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3147,65 +3240,68 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E44" s="3">
         <v>107900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>116700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>115400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>108500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>95200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>77200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>67800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>61800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>57600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>42200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>39600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>38700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>34100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>35500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>35100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>32300</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3320,11 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3253,44 +3352,44 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>18900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
-      </c>
-      <c r="V45" s="3">
-        <v>500</v>
       </c>
       <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
+      <c r="X45" s="3">
+        <v>500</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
@@ -3301,74 +3400,77 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1022900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1031300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1017200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1090600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1106200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1131200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1188300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1223900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1267400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1293800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1356800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1348900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1316500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1276800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1255500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1246100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1239100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>561000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>600</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,29 +3480,32 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E47" s="3">
         <v>9100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3416,8 +3521,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3431,18 +3536,18 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>345100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>345000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,65 +3560,68 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1289300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1261100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1240500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1226900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1206700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1168700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1108700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1055400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1002200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>935700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>830000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>749800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>668500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>611700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>584100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>562000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>534100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>503000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,37 +3640,40 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E49" s="3">
         <v>7400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -3573,8 +3684,8 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,65 +3880,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E52" s="3">
         <v>24700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>29200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>9800</v>
       </c>
       <c r="R52" s="3">
         <v>9800</v>
       </c>
       <c r="S52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="T52" s="3">
         <v>9300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,74 +4040,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2368100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2333600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2300300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2364300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2354000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2336500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2322200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2289400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2281100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2237800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2189200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2101200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1987200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1889700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1849500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1818000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1782500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1074300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>346300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>346900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>600</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,74 +4182,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E57" s="3">
         <v>23600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>92100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>71700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>68600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>72300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>70200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>37700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,38 +4260,41 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3700</v>
+        <v>72600</v>
       </c>
       <c r="E58" s="3">
         <v>3700</v>
       </c>
       <c r="F58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G58" s="3">
         <v>3200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4171,32 +4305,32 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>16300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>31200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>46100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>41800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>24700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4206,70 +4340,73 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E59" s="3">
         <v>98500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>89900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>111600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>59300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2200</v>
-      </c>
-      <c r="U59" s="3">
-        <v>100</v>
       </c>
       <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
+      <c r="W59" s="3">
+        <v>100</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
@@ -4283,74 +4420,77 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>248200</v>
+      </c>
+      <c r="E60" s="3">
         <v>164000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>146800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>158100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>107500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>108600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>97000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>75800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>97500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>74700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>66100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>51600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>59500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>70800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>90300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>72900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,65 +4500,68 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>860400</v>
+      </c>
+      <c r="E61" s="3">
         <v>915300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>945200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>944800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>944600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>691800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>691700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>691200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>683500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>678400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>677600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>676700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>675800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>675500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>674700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>673800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>691000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4437,70 +4580,73 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>25400</v>
+        <v>26000</v>
       </c>
       <c r="E62" s="3">
         <v>25400</v>
       </c>
       <c r="F62" s="3">
+        <v>25400</v>
+      </c>
+      <c r="G62" s="3">
         <v>25900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>22000</v>
       </c>
       <c r="J62" s="3">
         <v>22000</v>
       </c>
       <c r="K62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="L62" s="3">
         <v>22200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>149200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>194500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>187700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>169500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>145900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>149800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>147200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>143400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>131300</v>
-      </c>
-      <c r="U62" s="3">
-        <v>12100</v>
       </c>
       <c r="V62" s="3">
         <v>12100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="W62" s="3">
+        <v>12100</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,74 +4900,77 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1278700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1235700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1255300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1216300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>970700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>946100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>924500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>929300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>925200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>946900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>930500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>896800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>880900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>895300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>911300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>907400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>220400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>500</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,73 +5330,76 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>297700</v>
+      </c>
+      <c r="E72" s="3">
         <v>320300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>342600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>368200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>402200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>385700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>402000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>406300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>398900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>361400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>294400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>231200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>158000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>72400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>23400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-19300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-46500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-62600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-300</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,73 +5650,76 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1036100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1054900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1064500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1109000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1137800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1365800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1376100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1364900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1351800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1312600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1242300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1170700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1090400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1008700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>954200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>906600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>875200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>853900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>330700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>333800</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
+      <c r="X76" s="3">
+        <v>0</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,79 +5810,82 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,73 +5895,76 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>67000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>63200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>73300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>85600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>49000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>42800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,62 +6007,63 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E83" s="3">
         <v>18300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5880,14 +6079,17 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,73 +6485,76 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-63200</v>
+      </c>
+      <c r="E89" s="3">
         <v>30500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-41100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>55500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>94600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>121000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>31500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,62 +6597,63 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-41700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-73000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-74500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-112300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-91700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-67700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-54900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6448,14 +6669,17 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,67 +6835,70 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>20700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>40700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-269100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-390300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>265900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>462200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-315200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-325100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-666800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-49800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-25400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>322600</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6977,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,73 +7265,76 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-25300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>32900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>671800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>175200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>346800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
@@ -7099,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7377,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7176,73 +7425,76 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-284300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-380200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>275100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>510900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-290900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-231200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-568800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>53300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>662000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>502000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1400</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,112 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -771,68 +772,71 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E8" s="3">
         <v>60800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>61000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>62900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>31300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>48700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>52500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>64000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>95700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>93200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>124400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>143600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>166300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>99100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>99800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>73100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>60000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>134300</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,68 +855,71 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E9" s="3">
         <v>48800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>58300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>57300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>41500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>22100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>66200</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -931,68 +938,71 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E10" s="3">
         <v>12000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-10200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>17600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>68700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>102000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>121500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>143100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>80600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>77900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>55100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>42100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>68100</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1011,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,8 +1054,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,15 +1087,15 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>5600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1135,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,68 +1218,71 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-44800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>66600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1281,68 +1301,71 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E15" s="3">
         <v>21400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6900</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,76 +1414,77 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E17" s="3">
         <v>95200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>102500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>100600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>83200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>79700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>68500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>61900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>51200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>45700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>38300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>165600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
+      <c r="Y17" s="3">
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
@@ -1468,68 +1495,71 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-34400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-41500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-52000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-31000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>37400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>79100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>95800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>115100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>57100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>54100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-31300</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1578,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,68 +1611,69 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6700</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>11000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>3500</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,65 +1692,68 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-34100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-12800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>48200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>54000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>87400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>103400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>120500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>61100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>27900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,31 +1775,34 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E22" s="3">
         <v>7600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1400</v>
       </c>
       <c r="K22" s="3">
         <v>1400</v>
@@ -1771,35 +1811,35 @@
         <v>1400</v>
       </c>
       <c r="M22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>2600</v>
       </c>
       <c r="S22" s="3">
         <v>2600</v>
       </c>
       <c r="T22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5000</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,76 +1858,79 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-34900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-48200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>47100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>84100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>96600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>113300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>54700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>51600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-36100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
+      <c r="Y23" s="3">
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
@@ -1898,68 +1941,71 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-14100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-19900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>27800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-17600</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,76 +2107,79 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>67000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>73300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>85600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>42800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-18400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
+      <c r="Y26" s="3">
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
@@ -2138,76 +2190,79 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>67000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>63200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>73300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>85600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>49000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>42800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-18400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
+      <c r="Y27" s="3">
+        <v>0</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
@@ -2218,8 +2273,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,68 +2605,71 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>6700</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-11000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-3500</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,76 +2688,79 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>67000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>63200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>73300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>85600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>49000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>42800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-18400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
+      <c r="Y33" s="3">
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
@@ -2698,8 +2771,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,76 +2854,79 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>67000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>63200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>73300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>85600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>49000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>42800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-18400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
+      <c r="Y35" s="3">
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
@@ -2858,82 +2937,85 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2943,8 +3025,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,76 +3089,77 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>261500</v>
+      </c>
+      <c r="E41" s="3">
         <v>198300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>282400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>284400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>295600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>296500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>263400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>547700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>927200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>651200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>136600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>428000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>664500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1233300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1179300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1179400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1196900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1181500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>519700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1400</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
+      <c r="Y41" s="3">
+        <v>0</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
@@ -3083,50 +3170,53 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>492100</v>
+      </c>
+      <c r="E42" s="3">
         <v>560800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>568400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>582100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>641400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>650300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>734500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>537000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>200800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>517800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1045700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>836300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>599700</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3142,8 +3232,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3163,68 +3253,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E43" s="3">
         <v>113200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>62900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>31100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>35100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>37100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>51000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3600</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,68 +3336,71 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E44" s="3">
         <v>133100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>107900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>116700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>115400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>108500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>95200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>77200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>67800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>61800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>57600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>61600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>42200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>39600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>38700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>34100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>35500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>35100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>32300</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3323,8 +3419,11 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3355,44 +3454,44 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>18900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>500</v>
       </c>
       <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
+      <c r="Y45" s="3">
+        <v>500</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
@@ -3403,77 +3502,80 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>960400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1022900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1031300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1017200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1090600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1106200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1131200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1188300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1223900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1267400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1293800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1356800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1348900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1316500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1276800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1255500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1246100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1239100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>561000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,32 +3585,35 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>8800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9700</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,8 +3629,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3539,18 +3644,18 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>345100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>345000</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3563,68 +3668,71 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1289300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1261100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1240500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1226900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1206700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1168700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1108700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1055400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1002200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>935700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>830000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>749800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>668500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>611700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>584100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>562000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>534100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>503000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,40 +3751,43 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E49" s="3">
         <v>7100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9200</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -3687,8 +3798,8 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,68 +4000,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E52" s="3">
         <v>40100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1100</v>
-      </c>
-      <c r="R52" s="3">
-        <v>9800</v>
       </c>
       <c r="S52" s="3">
         <v>9800</v>
       </c>
       <c r="T52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="U52" s="3">
         <v>9300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,77 +4166,80 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2336200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2368100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2333600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2300300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2364300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2354000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2336500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2322200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2289400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2281100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2237800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2189200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2101200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1987200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1889700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1849500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1818000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1782500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1074300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>346300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>346900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>600</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,77 +4313,78 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E57" s="3">
         <v>20900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>92100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>71700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>68600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>70200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>37700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>27500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>16200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,41 +4394,44 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E58" s="3">
         <v>72600</v>
-      </c>
-      <c r="E58" s="3">
-        <v>3700</v>
       </c>
       <c r="F58" s="3">
         <v>3700</v>
       </c>
       <c r="G58" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H58" s="3">
         <v>3200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4308,32 +4442,32 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>16300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>31200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>46100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>41800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>24700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,73 +4477,76 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>129500</v>
+      </c>
+      <c r="E59" s="3">
         <v>125200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>98500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>89900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>111600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>59300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>49400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2200</v>
-      </c>
-      <c r="V59" s="3">
-        <v>100</v>
       </c>
       <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
+      <c r="X59" s="3">
+        <v>100</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
@@ -4423,77 +4560,80 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>266900</v>
+      </c>
+      <c r="E60" s="3">
         <v>248200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>164000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>146800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>158100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>107500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>108600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>97000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>75800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>93900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>97500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>74700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>51600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>59500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>70800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>90300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>72900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,68 +4643,71 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>872000</v>
+      </c>
+      <c r="E61" s="3">
         <v>860400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>915300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>945200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>944800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>944600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>691800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>691700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>691200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>683500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>678400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>677600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>676700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>675800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>675500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>674700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>673800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>691000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>46100</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4583,8 +4726,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4592,64 +4738,64 @@
         <v>26000</v>
       </c>
       <c r="E62" s="3">
-        <v>25400</v>
+        <v>26000</v>
       </c>
       <c r="F62" s="3">
         <v>25400</v>
       </c>
       <c r="G62" s="3">
+        <v>25400</v>
+      </c>
+      <c r="H62" s="3">
         <v>25900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>22000</v>
       </c>
       <c r="K62" s="3">
         <v>22000</v>
       </c>
       <c r="L62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="M62" s="3">
         <v>22200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>149200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>194500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>187700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>169500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>145900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>149800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>147200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>143400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>131300</v>
-      </c>
-      <c r="V62" s="3">
-        <v>12100</v>
       </c>
       <c r="W62" s="3">
         <v>12100</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
+      <c r="X62" s="3">
+        <v>12100</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,77 +5058,80 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1325600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1332000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1278700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1235700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1255300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1216300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>970700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>946100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>924500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>929300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>925200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>946900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>930500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>896800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>880900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>895300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>911300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>907400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>220400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,76 +5504,79 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>266800</v>
+      </c>
+      <c r="E72" s="3">
         <v>297700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>320300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>342600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>368200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>402200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>385700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>402000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>406300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>398900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>361400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>294400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>231200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>158000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>72400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>23400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-19300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-46500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-62600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-300</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
+      <c r="Y72" s="3">
+        <v>0</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,76 +5836,79 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1010600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1036100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1054900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1064500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1109000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1137800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1365800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1376100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1364900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1351800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1312600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1242300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1170700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1090400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1008700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>954200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>906600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>875200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>853900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>330700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>333800</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
+      <c r="Y76" s="3">
+        <v>0</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,82 +6002,85 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5898,76 +6090,79 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>67000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>63200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>73300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>85600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>49000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>42800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-18400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
+      <c r="Y81" s="3">
+        <v>0</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
@@ -5978,8 +6173,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,65 +6206,66 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E83" s="3">
         <v>18100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6082,14 +6281,17 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,76 +6702,79 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-63200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-41100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>55500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>94600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>98900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>121000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>31500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
+      <c r="Y89" s="3">
+        <v>0</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,65 +6818,66 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-41700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-73000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-74500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-112300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-91700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-67700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-54900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-41700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6672,14 +6893,17 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,70 +7065,73 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>20700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>40700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-269100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-390300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>265900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>462200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-315200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-325100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-666800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-25400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>322600</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6980,8 +7214,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,76 +7511,79 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-25300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>32900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>671800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>175200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>346800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
@@ -7348,8 +7594,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7380,8 +7629,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7428,76 +7677,79 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-83900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-284300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-380200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>275100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>510900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-290900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-231200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-568800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>53300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>662000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>502000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1400</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
+      <c r="Y102" s="3">
+        <v>0</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,120 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -779,74 +779,77 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>103700</v>
+      </c>
+      <c r="E8" s="3">
         <v>53600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>60800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>61000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>62900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>31300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>48700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>52500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>64000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>95700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>93200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>124400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>143600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>166300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>99100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>99800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>73100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>60000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>134300</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -865,74 +868,77 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E9" s="3">
         <v>48500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>50400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>48800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>58300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>57300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>41500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>35600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>22100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>23200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>66200</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -951,74 +957,77 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-10200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>41300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>71500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>102000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>121500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>143100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>80600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>77900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>55100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>42100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>68100</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1046,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,8 +1081,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,15 +1120,15 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3">
         <v>5600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2700</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1155,8 +1168,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,74 +1257,77 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E14" s="3">
         <v>9000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
-        <v>-4200</v>
-      </c>
       <c r="H14" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I14" s="3">
         <v>1900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-44800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>66600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1327,74 +1346,77 @@
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E15" s="3">
         <v>22500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>22100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>18400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>6900</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1413,8 +1435,11 @@
       <c r="AD15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,82 +1467,83 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>124800</v>
+      </c>
+      <c r="E17" s="3">
         <v>111600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>101500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>95200</v>
       </c>
-      <c r="G17" s="3">
-        <v>102500</v>
-      </c>
       <c r="H17" s="3">
+        <v>102900</v>
+      </c>
+      <c r="I17" s="3">
         <v>100600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>83200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>79700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>68500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>61900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>57100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>45300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>47800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>51200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>42000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>45700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>38300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>165600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
+      <c r="AA17" s="3">
+        <v>0</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
@@ -1528,74 +1554,77 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-58100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-44100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-41500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-37600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-52000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>79100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>95800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>115100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>57100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>54100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-31300</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1614,8 +1643,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,74 +1678,75 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6700</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>11000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>3500</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,71 +1765,74 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-34900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-24900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-19400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-18700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-34100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>48200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>54000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>87400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>103400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>120500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>61800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>61100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>27900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,37 +1854,40 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="3">
         <v>8600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1400</v>
       </c>
       <c r="M22" s="3">
         <v>1400</v>
@@ -1857,35 +1896,35 @@
         <v>1400</v>
       </c>
       <c r="O22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2500</v>
-      </c>
-      <c r="T22" s="3">
-        <v>2600</v>
       </c>
       <c r="U22" s="3">
         <v>2600</v>
       </c>
       <c r="V22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="W22" s="3">
         <v>1200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5000</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1904,82 +1943,85 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-58400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-42700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-34000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-48200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>47100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>84100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>96600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>113300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>54700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>51600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>33300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>20600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-36100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
+      <c r="AA23" s="3">
+        <v>0</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
@@ -1990,74 +2032,77 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-16700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-11600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-9400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-14100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-19900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>27800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-17600</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2076,8 +2121,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,82 +2210,85 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-41800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-22600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>67000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>63200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>73300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>85600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>49000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>42800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-18400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
+      <c r="AA26" s="3">
+        <v>0</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
@@ -2248,82 +2299,85 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-41800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>67000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>63200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>73300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>85600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>49000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>42800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-18400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
+      <c r="AA27" s="3">
+        <v>0</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
@@ -2334,8 +2388,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2477,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2566,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2655,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,74 +2744,77 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6700</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-11000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-3500</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,82 +2833,85 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-41800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-30900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>67000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>63200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>73300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>85600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>49000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>42800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-18400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
+      <c r="AA33" s="3">
+        <v>0</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
@@ -2850,8 +2922,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,82 +3011,85 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-41800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-30900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>67000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>63200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>73300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>85600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>49000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>42800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-18400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
+      <c r="AA35" s="3">
+        <v>0</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
@@ -3022,88 +3100,91 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3113,8 +3194,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3229,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,82 +3262,83 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1166000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1147200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>261500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>198300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>282400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>284400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>295600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>296500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>263400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>547700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>927200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>651200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>136600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>428000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>664500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1233300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1179300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1179400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1196900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1181500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>519700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1400</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
+      <c r="AA41" s="3">
+        <v>0</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
@@ -3263,56 +3349,59 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>664300</v>
+      </c>
+      <c r="E42" s="3">
         <v>793200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>492100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>560800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>568400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>582100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>641400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>650300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>734500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>537000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>200800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>517800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1045700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>836300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>599700</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3328,8 +3417,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3349,74 +3438,77 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E43" s="3">
         <v>74500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>64900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>62900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>31100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>35100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>51000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>37100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3600</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3435,74 +3527,77 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>171600</v>
+      </c>
+      <c r="E44" s="3">
         <v>144400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>128000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>133100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>107900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>115400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>108500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>95200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>77200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>67800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>61800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>57600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>61600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>42200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>39600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>38700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>34100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>35500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>35100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>32300</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,8 +3616,11 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3559,44 +3657,44 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>18900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>500</v>
       </c>
       <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
+      <c r="AA45" s="3">
+        <v>500</v>
       </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
@@ -3607,83 +3705,86 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2165800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2174400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>960400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1022900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1031300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1017200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1090600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1106200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1131200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1188300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1223900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1267400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1293800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1356800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1348900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1316500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1276800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1255500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1246100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1239100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>561000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>600</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,8 +3794,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3704,27 +3808,27 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>8800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9700</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3740,8 +3844,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3755,18 +3859,18 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3">
         <v>345100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>345000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3779,74 +3883,77 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1383000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1320300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1289300</v>
       </c>
-      <c r="G48" s="3">
-        <v>1261100</v>
-      </c>
       <c r="H48" s="3">
+        <v>1260200</v>
+      </c>
+      <c r="I48" s="3">
         <v>1240500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1226900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1206700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1168700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1108700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1055400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1002200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>935700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>830000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>749800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>668500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>611700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>584100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>562000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>534100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>503000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,46 +3972,49 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E49" s="3">
         <v>6500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9200</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -3915,8 +4025,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3951,8 +4061,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4150,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,74 +4239,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>306900</v>
+      </c>
+      <c r="E52" s="3">
         <v>297200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>69000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>24700</v>
       </c>
       <c r="H52" s="3">
         <v>25600</v>
       </c>
       <c r="I52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="J52" s="3">
         <v>29200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1100</v>
-      </c>
-      <c r="T52" s="3">
-        <v>9800</v>
       </c>
       <c r="U52" s="3">
         <v>9800</v>
       </c>
       <c r="V52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="W52" s="3">
         <v>9300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4328,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,83 +4417,86 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3864200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3798300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2336200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2368100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2333600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2300300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2364300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2354000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2336500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2322200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2289400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2281100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2237800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2189200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2101200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1987200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1889700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1849500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1818000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1782500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1074300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>346300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>346900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4506,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4541,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,83 +4574,84 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E57" s="3">
         <v>25400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>92100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>71700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>68600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>72300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>70200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>62100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>35700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>27800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>37700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>27500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,8 +4661,11 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4540,38 +4673,38 @@
         <v>74500</v>
       </c>
       <c r="E58" s="3">
+        <v>74500</v>
+      </c>
+      <c r="F58" s="3">
         <v>72800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>72600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2300</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4582,32 +4715,32 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>16300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>31200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>46100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>41800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>24700</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4617,79 +4750,82 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E59" s="3">
         <v>134700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>129500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>125200</v>
       </c>
-      <c r="G59" s="3">
-        <v>98500</v>
-      </c>
       <c r="H59" s="3">
+        <v>101800</v>
+      </c>
+      <c r="I59" s="3">
         <v>94800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>115000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>59300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>49400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2200</v>
-      </c>
-      <c r="X59" s="3">
-        <v>100</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
+      <c r="Z59" s="3">
+        <v>100</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
@@ -4703,83 +4839,86 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>296600</v>
+      </c>
+      <c r="E60" s="3">
         <v>270200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>266900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>248200</v>
       </c>
-      <c r="G60" s="3">
-        <v>164000</v>
-      </c>
       <c r="H60" s="3">
+        <v>161900</v>
+      </c>
+      <c r="I60" s="3">
         <v>146800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>158100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>107500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>108600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>97000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>75800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>93900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>97500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>74700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>66100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>51600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>59500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>70800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>90300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>72900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>500</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,74 +4928,77 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>960100</v>
+      </c>
+      <c r="E61" s="3">
         <v>960400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>872000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>860400</v>
       </c>
-      <c r="G61" s="3">
-        <v>915300</v>
-      </c>
       <c r="H61" s="3">
+        <v>915100</v>
+      </c>
+      <c r="I61" s="3">
         <v>945200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>944800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>944600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>691800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>691700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>691200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>683500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>678400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>677600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>676700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>675800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>675500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>674700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>673800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>691000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>46100</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4875,79 +5017,82 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E62" s="3">
         <v>27500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>26000</v>
       </c>
       <c r="F62" s="3">
         <v>26000</v>
       </c>
       <c r="G62" s="3">
+        <v>26000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>25600</v>
+      </c>
+      <c r="I62" s="3">
         <v>25400</v>
       </c>
-      <c r="H62" s="3">
-        <v>25400</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22100</v>
-      </c>
-      <c r="L62" s="3">
-        <v>22000</v>
       </c>
       <c r="M62" s="3">
         <v>22000</v>
       </c>
       <c r="N62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="O62" s="3">
         <v>22200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>149200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>194500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>187700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>169500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>145900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>149800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>147200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>143400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>131300</v>
-      </c>
-      <c r="X62" s="3">
-        <v>12100</v>
       </c>
       <c r="Y62" s="3">
         <v>12100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
+      <c r="Z62" s="3">
+        <v>12100</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
@@ -4961,8 +5106,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5195,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5284,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,83 +5373,86 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1471800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1419900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1325600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1332000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1278700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1235700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1255300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1216300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>970700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>946100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>924500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>929300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>925200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>946900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>930500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>896800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>880900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>895300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>911300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>907400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>220400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>500</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5462,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5497,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5584,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5673,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5518,7 +5685,7 @@
         <v>413600</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>413600</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -5595,8 +5762,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,82 +5851,85 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>234400</v>
+      </c>
+      <c r="E72" s="3">
         <v>225000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>266800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>297700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>320300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>342600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>368200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>402200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>385700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>402000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>406300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>398900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>361400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>294400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>231200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>158000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>72400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>23400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-19300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-46500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-62600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-300</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
+      <c r="AA72" s="3">
+        <v>0</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
@@ -5767,8 +5940,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6029,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6118,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,82 +6207,85 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1978800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1964800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1010600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1036100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1054900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1064500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1109000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1137800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1365800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1376100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1364900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1351800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1312600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1242300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1170700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1090400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1008700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>954200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>906600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>875200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>853900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>330700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>333800</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
+      <c r="AA76" s="3">
+        <v>0</v>
       </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
@@ -6111,8 +6296,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,88 +6385,91 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6288,82 +6479,85 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-41800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-30900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>67000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>63200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>73300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>85600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>49000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>42800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-18400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
+      <c r="AA81" s="3">
+        <v>0</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
@@ -6374,8 +6568,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,71 +6603,72 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E83" s="3">
         <v>19000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6200</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,14 +6684,17 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6779,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6868,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6957,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7046,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,82 +7135,85 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-42000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-63200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>30800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-41100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>55500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>94600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>98900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>121000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>38600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
+      <c r="AA89" s="3">
+        <v>0</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
@@ -7008,8 +7224,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,71 +7259,72 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-50500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-46400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-73000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-58700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-74500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-112300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-91700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-67700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-54900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-37500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-25400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7120,14 +7340,17 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7435,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,76 +7524,79 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-333100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>69700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>20700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>40700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-269100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-390300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>265900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>462200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-315200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-325100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-666800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-39100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-25400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>322600</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -7384,8 +7613,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7648,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7454,8 +7687,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7502,8 +7735,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7824,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7913,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,82 +8002,85 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1260600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-25300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>32900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>671800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>175200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>346800</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
@@ -7846,8 +8091,11 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7884,8 +8132,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7932,82 +8180,85 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E102" s="3">
         <v>885500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>63300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-83900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>32500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-284300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-380200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>275100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>510900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-290900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-231200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-568800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>53300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>662000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>502000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1400</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
+      <c r="AA102" s="3">
+        <v>0</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
@@ -8016,6 +8267,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
   <si>
     <t>MP</t>
   </si>
@@ -656,123 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -782,77 +783,80 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>132900</v>
+      </c>
+      <c r="E8" s="3">
         <v>103700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>57400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>60800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>61000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>62900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>31300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>48700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>41200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>52500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>64000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>95700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>93200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>124400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>143600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>166300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>99100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>99800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>73100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>60000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>134300</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,77 +875,80 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E9" s="3">
         <v>45100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>48500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>50400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>48800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>58300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>57300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>41500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>23600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>22400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>22100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>23200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>66200</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,8 +967,11 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -969,68 +979,68 @@
         <v>58700</v>
       </c>
       <c r="E10" s="3">
+        <v>58700</v>
+      </c>
+      <c r="F10" s="3">
         <v>5100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-10200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>17600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>41300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>102000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>121500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>143100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>80600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>77900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>55100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>42100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>68100</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1049,8 +1059,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1082,8 +1095,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,15 +1137,15 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
         <v>5600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2700</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,8 +1185,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1260,77 +1277,80 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-17400</v>
+        <v>13700</v>
       </c>
       <c r="E14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F14" s="3">
         <v>9000</v>
       </c>
-      <c r="F14" s="3">
-        <v>-200</v>
-      </c>
       <c r="G14" s="3">
-        <v>400</v>
+        <v>-1000</v>
       </c>
       <c r="H14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-4600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-44800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6800</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1800</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
         <v>66600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,77 +1369,80 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E15" s="3">
         <v>24600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>21400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>22100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>18200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>7000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>6200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>6900</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,8 +1461,11 @@
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1468,85 +1494,86 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>124800</v>
+        <v>143400</v>
       </c>
       <c r="E17" s="3">
+        <v>104700</v>
+      </c>
+      <c r="F17" s="3">
         <v>111600</v>
       </c>
-      <c r="F17" s="3">
-        <v>101500</v>
-      </c>
       <c r="G17" s="3">
-        <v>95200</v>
+        <v>102300</v>
       </c>
       <c r="H17" s="3">
+        <v>92600</v>
+      </c>
+      <c r="I17" s="3">
         <v>102900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>83200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>79700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>68500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>61900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>45300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>51200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>45700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>40700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>38300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>165600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="AA17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
+      <c r="AB17" s="3">
+        <v>0</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
@@ -1557,77 +1584,80 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-21100</v>
+        <v>-10500</v>
       </c>
       <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-58100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-44100</v>
-      </c>
       <c r="G18" s="3">
-        <v>-34400</v>
+        <v>-44900</v>
       </c>
       <c r="H18" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-41900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-37600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-52000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-31000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-27300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>79100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>95800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>115100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>57100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>54100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-31300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,8 +1676,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1679,77 +1712,78 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6700</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>11000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>3500</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1768,74 +1802,77 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>8900</v>
+        <v>26400</v>
       </c>
       <c r="E21" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-34900</v>
       </c>
-      <c r="F21" s="3">
-        <v>-24900</v>
-      </c>
       <c r="G21" s="3">
-        <v>-6400</v>
+        <v>-25700</v>
       </c>
       <c r="H21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-19700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>48200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>54000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>87400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>103400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>120500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>61800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>61100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>27900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1857,40 +1894,43 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E22" s="3">
         <v>9900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1400</v>
       </c>
       <c r="N22" s="3">
         <v>1400</v>
@@ -1899,35 +1939,35 @@
         <v>1400</v>
       </c>
       <c r="P22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>2600</v>
       </c>
       <c r="V22" s="3">
         <v>2600</v>
       </c>
       <c r="W22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X22" s="3">
         <v>1200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5000</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1946,85 +1986,88 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E23" s="3">
         <v>10600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-58400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-42700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-34900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-48200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>47100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>84100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>96600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>113300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>54700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>51600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>33300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
+      <c r="AB23" s="3">
+        <v>0</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
@@ -2035,77 +2078,80 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-11900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-11600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-9400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-14100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>20900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>27800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2124,8 +2170,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2213,85 +2262,88 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E26" s="3">
         <v>9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-41800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-30900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-22300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>67000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>63200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>73300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>85600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>49000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
+      <c r="AB26" s="3">
+        <v>0</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
@@ -2302,85 +2354,88 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-41800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-30900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-22300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>67000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>63200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>73300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>85600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
+      <c r="AB27" s="3">
+        <v>0</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
@@ -2391,8 +2446,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2480,8 +2538,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2569,8 +2630,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2658,8 +2722,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2747,77 +2814,80 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E32" s="3">
         <v>5300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6700</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-3500</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,85 +2906,88 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-41800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-30900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-22300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>67000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>63200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>73300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>85600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>49000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>42800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
+      <c r="AB33" s="3">
+        <v>0</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
@@ -2925,8 +2998,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3014,85 +3090,88 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-41800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-30900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-22300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>67000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>63200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>73300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>85600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>49000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>42800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
+      <c r="AB35" s="3">
+        <v>0</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
@@ -3103,91 +3182,94 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3197,8 +3279,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3230,8 +3315,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3263,85 +3349,86 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>886300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1166000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1147200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>261500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>198300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>282400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>284400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>295600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>296500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>263400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>547700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>927200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>651200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>136600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>428000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>664500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1233300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1179300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1179400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1196900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1181500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>519700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1400</v>
       </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
+      <c r="AB41" s="3">
+        <v>0</v>
       </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
@@ -3352,59 +3439,62 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>852100</v>
+      </c>
+      <c r="E42" s="3">
         <v>664300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>793200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>492100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>560800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>568400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>582100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>641400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>650300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>734500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>537000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>200800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>517800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1045700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>836300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>599700</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3420,8 +3510,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3441,77 +3531,80 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>119300</v>
+      </c>
+      <c r="E43" s="3">
         <v>146700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>74500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>64900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>62900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>31100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>35100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>19900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>37100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>51000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>37100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3600</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,77 +3623,80 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>169200</v>
+      </c>
+      <c r="E44" s="3">
         <v>171600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>144400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>128000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>133100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>107900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>116700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>115400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>108500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>95200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>77200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>67800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>61800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>57600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>42200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>39600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>38700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>34100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>35500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>35100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>32300</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3619,8 +3715,11 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3660,44 +3759,44 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>18900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>500</v>
       </c>
       <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
+      <c r="AB45" s="3">
+        <v>500</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
@@ -3708,86 +3807,89 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2046900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2165800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2174400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>960400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1022900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1031300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1017200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1090600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1106200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1131200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1188300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1223900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1267400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1293800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1356800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1348900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1316500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1276800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1255500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1246100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1239100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>561000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>600</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,8 +3899,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3811,27 +3916,27 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>8800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,8 +3952,8 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3862,18 +3967,18 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3">
         <v>345100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>345000</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3886,77 +3991,80 @@
       <c r="AE47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1452800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1383000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1320300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1289300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1260200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1240500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1226900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1206700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1168700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1108700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1055400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1002200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>935700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>830000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>749800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>668500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>611700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>584100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>562000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>534100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>503000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3975,49 +4083,52 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>6200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9200</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -4028,8 +4139,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -4064,8 +4175,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4153,8 +4267,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4242,77 +4359,80 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>336300</v>
+      </c>
+      <c r="E52" s="3">
         <v>306900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>297200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>69000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>25600</v>
       </c>
       <c r="I52" s="3">
         <v>25600</v>
       </c>
       <c r="J52" s="3">
+        <v>25600</v>
+      </c>
+      <c r="K52" s="3">
         <v>29200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1100</v>
-      </c>
-      <c r="U52" s="3">
-        <v>9800</v>
       </c>
       <c r="V52" s="3">
         <v>9800</v>
       </c>
       <c r="W52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="X52" s="3">
         <v>9300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4331,8 +4451,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4420,86 +4543,89 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3840200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3864200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3798300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2336200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2368100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2333600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2300300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2364300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2354000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2336500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2322200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2289400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2281100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2237800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2189200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2101200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1987200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1889700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1849500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1818000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1782500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1074300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>346300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>346900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>600</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4509,8 +4635,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4542,8 +4671,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4575,86 +4705,87 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E57" s="3">
         <v>36700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>26100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>92100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>71700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>68600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>72300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>70200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>62100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>35700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>27800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>37700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>27500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>16200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,50 +4795,53 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>74500</v>
+        <v>76200</v>
       </c>
       <c r="E58" s="3">
         <v>74500</v>
       </c>
       <c r="F58" s="3">
+        <v>74500</v>
+      </c>
+      <c r="G58" s="3">
         <v>72800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>72600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2300</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4718,32 +4852,32 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>16300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>31200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>46100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>41800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>24700</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB58" s="3">
         <v>200</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4753,82 +4887,85 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>138300</v>
+      </c>
+      <c r="E59" s="3">
         <v>144100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>134700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>129500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>125200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>101800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>94800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>115000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>59300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>49400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>23000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>100</v>
       </c>
       <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
+      <c r="AA59" s="3">
+        <v>100</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
@@ -4842,86 +4979,89 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>285300</v>
+      </c>
+      <c r="E60" s="3">
         <v>296600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>270200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>266900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>248200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>161900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>146800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>158100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>107500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>108600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>97000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>75800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>93900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>97500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>74700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>66100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>51600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>59500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>70800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>90300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>72900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>43100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>500</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4931,77 +5071,80 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>971700</v>
+      </c>
+      <c r="E61" s="3">
         <v>960100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>960400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>872000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>860400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>915100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>945200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>944800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>944600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>691800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>691700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>691200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>683500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>678400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>677600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>676700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>675800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>675500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>674700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>673800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>691000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>46100</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5020,82 +5163,85 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E62" s="3">
         <v>28200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>26000</v>
       </c>
       <c r="G62" s="3">
         <v>26000</v>
       </c>
       <c r="H62" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I62" s="3">
         <v>25600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>22000</v>
       </c>
       <c r="N62" s="3">
         <v>22000</v>
       </c>
       <c r="O62" s="3">
+        <v>22000</v>
+      </c>
+      <c r="P62" s="3">
         <v>22200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>149200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>194500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>187700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>169500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>145900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>149800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>147200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>143400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>131300</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>12100</v>
       </c>
       <c r="Z62" s="3">
         <v>12100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
+      <c r="AA62" s="3">
+        <v>12100</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
@@ -5109,8 +5255,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5198,8 +5347,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5287,8 +5439,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5376,86 +5531,89 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1459400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1471800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1419900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1325600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1332000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1278700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1235700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1255300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1216300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>970700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>946100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>924500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>929300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>925200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>946900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>930500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>896800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>880900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>895300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>911300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>907400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>220400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5465,8 +5623,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5498,8 +5659,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5587,8 +5749,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5676,8 +5841,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5688,7 +5856,7 @@
         <v>413600</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>413600</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -5765,8 +5933,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5854,85 +6025,88 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>226500</v>
+      </c>
+      <c r="E72" s="3">
         <v>234400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>225000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>266800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>297700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>320300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>342600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>368200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>402200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>385700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>402000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>406300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>398900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>361400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>294400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>231200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>158000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>72400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>23400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-19300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-46500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-62600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-300</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
+      <c r="AB72" s="3">
+        <v>0</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
@@ -5943,8 +6117,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6032,8 +6209,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6121,8 +6301,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6210,85 +6393,88 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1967100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1978800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1964800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1010600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1036100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1054900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1064500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1109000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1137800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1365800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1376100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1364900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1351800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1312600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1242300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1170700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1090400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1008700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>954200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>906600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>875200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>853900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>330700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>333800</v>
       </c>
-      <c r="AA76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
+      <c r="AB76" s="3">
+        <v>0</v>
       </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
@@ -6299,8 +6485,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6388,91 +6577,94 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6482,85 +6674,88 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-41800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-30900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-22300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>67000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>63200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>73300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>85600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>49000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>42800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
+      <c r="AB81" s="3">
+        <v>0</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
@@ -6571,8 +6766,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6604,8 +6802,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6613,65 +6812,65 @@
         <v>21400</v>
       </c>
       <c r="E83" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F83" s="3">
         <v>19000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>18000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6687,14 +6886,17 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6782,8 +6984,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6871,8 +7076,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6960,8 +7168,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7049,8 +7260,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7138,85 +7352,88 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-46900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-42000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-63200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>30500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-41100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>55500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>94600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>98900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>121000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>22500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
+      <c r="AB89" s="3">
+        <v>0</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
@@ -7227,8 +7444,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7260,74 +7480,75 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-62400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-50500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-41700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-51800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-73000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-58700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-74500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-112300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-91700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-67700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-54900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-37500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-41700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7343,14 +7564,17 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7438,8 +7662,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7527,79 +7754,82 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-259800</v>
+      </c>
+      <c r="E94" s="3">
         <v>73000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-333100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>69700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>20700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>40700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-269100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-390300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>265900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>462200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-315200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-325100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-666800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-49800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-39100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-25400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>322600</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
@@ -7616,8 +7846,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7649,8 +7882,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7690,8 +7924,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7738,8 +7972,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7827,8 +8064,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7916,8 +8156,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8005,85 +8248,88 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1260600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>32900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>671800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>175200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>346800</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
@@ -8094,8 +8340,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8135,8 +8384,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8183,85 +8432,88 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-280300</v>
+      </c>
+      <c r="E102" s="3">
         <v>18900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>885500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>63300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-83900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>32500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-284300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-380200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>275100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>510900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-290900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-231200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-568800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>53300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>11900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>662000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>502000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1400</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
+      <c r="AB102" s="3">
+        <v>0</v>
       </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
@@ -8270,6 +8522,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
